--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB59302C-4ED6-9F47-AC95-767242C1FBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A7366B-1972-8641-946D-C8ED8D2FB3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4900" yWindow="-17000" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="-500" yWindow="-19420" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="215">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -672,6 +672,15 @@
   </si>
   <si>
     <t>16.08.2026</t>
+  </si>
+  <si>
+    <t>Matchday 18</t>
+  </si>
+  <si>
+    <t>AIK Solna (H) 3:2</t>
+  </si>
+  <si>
+    <t>30.08.2026</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK22"/>
+  <dimension ref="A1:RK23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4313,7 +4322,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G22" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G23" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21235,6 +21244,45 @@
       </c>
       <c r="L22">
         <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" t="s">
+        <v>213</v>
+      </c>
+      <c r="C23" t="s">
+        <v>214</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F23">
+        <v>1.56</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>-2.5399999999999996</v>
+      </c>
+      <c r="H23">
+        <v>61</v>
+      </c>
+      <c r="I23">
+        <v>360</v>
+      </c>
+      <c r="J23">
+        <v>99</v>
+      </c>
+      <c r="K23">
+        <v>8</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A7366B-1972-8641-946D-C8ED8D2FB3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6D70E9-B182-254B-9A53-978BEA728553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-500" yWindow="-19420" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="3140" yWindow="1720" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="217">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -681,6 +681,12 @@
   </si>
   <si>
     <t>30.08.2026</t>
+  </si>
+  <si>
+    <t>Matchday 19</t>
+  </si>
+  <si>
+    <t>07.09.2026</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK23"/>
+  <dimension ref="A1:RK24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4322,7 +4328,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G23" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G24" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21283,6 +21289,45 @@
       </c>
       <c r="L23">
         <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" t="s">
+        <v>216</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24">
+        <v>0.89</v>
+      </c>
+      <c r="F24">
+        <v>0.71</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>-0.18000000000000005</v>
+      </c>
+      <c r="H24">
+        <v>49</v>
+      </c>
+      <c r="I24">
+        <v>284</v>
+      </c>
+      <c r="J24">
+        <v>123</v>
+      </c>
+      <c r="K24">
+        <v>6</v>
+      </c>
+      <c r="L24">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6D70E9-B182-254B-9A53-978BEA728553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B28F8F-15A6-BF43-8B61-BB1AE0610EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3140" yWindow="1720" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="3220" yWindow="-19580" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="220">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -687,6 +687,15 @@
   </si>
   <si>
     <t>07.09.2026</t>
+  </si>
+  <si>
+    <t>Matchday 20</t>
+  </si>
+  <si>
+    <t>AIK Solna (H) 1:4</t>
+  </si>
+  <si>
+    <t>12.09.2026</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK24"/>
+  <dimension ref="A1:RK25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4328,7 +4337,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G24" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G25" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21328,6 +21337,45 @@
       </c>
       <c r="L24">
         <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" t="s">
+        <v>218</v>
+      </c>
+      <c r="C25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>1.75</v>
+      </c>
+      <c r="F25">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>0.29999999999999982</v>
+      </c>
+      <c r="H25">
+        <v>54</v>
+      </c>
+      <c r="I25">
+        <v>434</v>
+      </c>
+      <c r="J25">
+        <v>170</v>
+      </c>
+      <c r="K25">
+        <v>17</v>
+      </c>
+      <c r="L25">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B28F8F-15A6-BF43-8B61-BB1AE0610EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5DC727-E4C4-264F-A2FE-41619531C8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3220" yWindow="-19580" windowWidth="27640" windowHeight="16940" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23580" windowHeight="21680" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="221">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -696,6 +696,9 @@
   </si>
   <si>
     <t>12.09.2026</t>
+  </si>
+  <si>
+    <t>Matchday 21</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK25"/>
+  <dimension ref="A1:RK26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4337,7 +4340,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G25" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G26" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21376,6 +21379,45 @@
       </c>
       <c r="L25">
         <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26">
+        <v>1.52</v>
+      </c>
+      <c r="F26">
+        <v>2.48</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>0.96</v>
+      </c>
+      <c r="H26">
+        <v>69</v>
+      </c>
+      <c r="I26">
+        <v>437</v>
+      </c>
+      <c r="J26">
+        <v>125</v>
+      </c>
+      <c r="K26">
+        <v>12</v>
+      </c>
+      <c r="L26">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5DC727-E4C4-264F-A2FE-41619531C8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E277ACB5-B5C6-DE4B-859E-B71D1374E450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="23580" windowHeight="21680" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="-2000" yWindow="700" windowWidth="23580" windowHeight="21680" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="223">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -699,6 +699,12 @@
   </si>
   <si>
     <t>Matchday 21</t>
+  </si>
+  <si>
+    <t>Matchday 22</t>
+  </si>
+  <si>
+    <t>20.09.2026</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK26"/>
+  <dimension ref="A1:RK27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4340,7 +4346,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G26" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G27" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21418,6 +21424,45 @@
       </c>
       <c r="L26">
         <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>222</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27">
+        <v>2.86</v>
+      </c>
+      <c r="F27">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>-0.67999999999999972</v>
+      </c>
+      <c r="H27">
+        <v>66</v>
+      </c>
+      <c r="I27">
+        <v>458</v>
+      </c>
+      <c r="J27">
+        <v>130</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
+      <c r="L27">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E277ACB5-B5C6-DE4B-859E-B71D1374E450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4BF528-6695-2446-A920-F65B52AD98B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2000" yWindow="700" windowWidth="23580" windowHeight="21680" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="7780" yWindow="-20880" windowWidth="23580" windowHeight="21000" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="226">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -705,6 +705,15 @@
   </si>
   <si>
     <t>20.09.2026</t>
+  </si>
+  <si>
+    <t>Matchday 23</t>
+  </si>
+  <si>
+    <t>AIK Solna (H) 5:6</t>
+  </si>
+  <si>
+    <t>10.10.2026</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK27"/>
+  <dimension ref="A1:RK28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4346,7 +4355,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G27" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G28" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21463,6 +21472,45 @@
       </c>
       <c r="L27">
         <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" t="s">
+        <v>224</v>
+      </c>
+      <c r="C28" t="s">
+        <v>225</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28">
+        <v>3.12</v>
+      </c>
+      <c r="F28">
+        <v>2.61</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>-0.51000000000000023</v>
+      </c>
+      <c r="H28">
+        <v>59</v>
+      </c>
+      <c r="I28">
+        <v>444</v>
+      </c>
+      <c r="J28">
+        <v>180</v>
+      </c>
+      <c r="K28">
+        <v>15</v>
+      </c>
+      <c r="L28">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/6_KPI_Match_by_match.xlsx
+++ b/data/6_KPI_Match_by_match.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulkaminiczny/Downloads/aik-kpi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4BF528-6695-2446-A920-F65B52AD98B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3305C833-F23F-7B4F-B75D-F00FBC087AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7780" yWindow="-20880" windowWidth="23580" windowHeight="21000" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
+    <workbookView xWindow="7780" yWindow="-21000" windowWidth="23580" windowHeight="21000" xr2:uid="{CB4CD926-A2C0-9B40-A78F-204678DF6140}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="229">
   <si>
     <t>Matchday SvC1</t>
   </si>
@@ -714,6 +714,15 @@
   </si>
   <si>
     <t>10.10.2026</t>
+  </si>
+  <si>
+    <t>Matchday 24</t>
+  </si>
+  <si>
+    <t>AIK Solna (H) 2:2</t>
+  </si>
+  <si>
+    <t>17.10.2026</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9DCE45-8537-994C-8254-C5FF7419F7E2}">
-  <dimension ref="A1:RK28"/>
+  <dimension ref="A1:RK29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -4355,7 +4364,7 @@
         <v>1.62</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G28" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G29" si="0">F3-E3</f>
         <v>0.78000000000000014</v>
       </c>
       <c r="H3">
@@ -21511,6 +21520,45 @@
       </c>
       <c r="L28">
         <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29">
+        <v>1.46</v>
+      </c>
+      <c r="F29">
+        <v>1.9</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>0.43999999999999995</v>
+      </c>
+      <c r="H29">
+        <v>52</v>
+      </c>
+      <c r="I29">
+        <v>338</v>
+      </c>
+      <c r="J29">
+        <v>158</v>
+      </c>
+      <c r="K29">
+        <v>8</v>
+      </c>
+      <c r="L29">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
